--- a/SGC-CKN/Excel/1fe63a4b-da72-4c46-997f-b8dcd4ac221b_Thi_công_cọc_khoan_nhồi_P1-71_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/1fe63a4b-da72-4c46-997f-b8dcd4ac221b_Thi_công_cọc_khoan_nhồi_P1-71_D800_05-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -115,10 +115,8 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t>17:56</t>
-  </si>
-  <si>
-    <t>18:20</t>
+    <t xml:space="preserve">18:20
+04/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -127,7 +125,8 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t>19:30</t>
+    <t xml:space="preserve">19:30
+04/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,10 +135,8 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t>19:36</t>
-  </si>
-  <si>
-    <t>21:30</t>
+    <t xml:space="preserve">21:30
+04/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -148,7 +145,8 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t>23:40</t>
+    <t xml:space="preserve">23:40
+04/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -157,7 +155,8 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t>00:20</t>
+    <t xml:space="preserve">00:20
+05/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,22 +165,18 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t>02:18</t>
+    <t xml:space="preserve">02:18
+05/04/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>undefined</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t>05:28</t>
+    <t xml:space="preserve">05:28
+05/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -340,12 +335,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -501,17 +496,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,7 +585,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -950,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1153,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.18</v>
+        <v>-3.78</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>3.18</v>
+        <v>3.78</v>
       </c>
       <c r="J11" s="8">
-        <v>9.54</v>
+        <v>11.34</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1179,95 +1174,95 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" s="9">
-        <v>-3.18</v>
+        <v>-3.78</v>
       </c>
       <c r="G12" s="9">
-        <v>-3.78</v>
+        <v>-6.88</v>
       </c>
       <c r="H12" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="J12" s="12">
-        <v>1.5</v>
+        <v>3.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>6.2</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="13">
-        <v>-3.78</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="F13" s="12">
         <v>-6.88</v>
       </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-10.18</v>
+      </c>
+      <c r="H13" s="12">
         <v>1.17</v>
       </c>
-      <c r="I13" s="13">
-        <v>3.1</v>
-      </c>
-      <c r="J13" s="12">
-        <v>2.66</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="I13" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="J13" s="15">
+        <v>2.83</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="16">
-        <v>-6.88</v>
+        <v>-10.18</v>
       </c>
       <c r="G14" s="16">
-        <v>-10.18</v>
+        <v>-18.98</v>
       </c>
       <c r="H14" s="16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I14" s="16">
-        <v>3.3</v>
-      </c>
-      <c r="J14" s="12">
-        <v>1.74</v>
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="15">
+        <v>4.4</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1275,34 +1270,34 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-10.18</v>
+        <v>-18.98</v>
       </c>
       <c r="G15" s="19">
-        <v>-18.98</v>
+        <v>-21.48</v>
       </c>
       <c r="H15" s="19">
         <v>2.17</v>
       </c>
       <c r="I15" s="19">
-        <v>8.8</v>
-      </c>
-      <c r="J15" s="12">
-        <v>4.06</v>
+        <v>2.5</v>
+      </c>
+      <c r="J15" s="15">
+        <v>1.15</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1310,34 +1305,34 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>-18.98</v>
+        <v>-21.48</v>
       </c>
       <c r="G16" s="22">
-        <v>-24.98</v>
+        <v>-28.48</v>
       </c>
       <c r="H16" s="22">
         <v>0.67</v>
       </c>
       <c r="I16" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="8">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1345,124 +1340,90 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-24.98</v>
+        <v>-28.48</v>
       </c>
       <c r="G17" s="25">
-        <v>-28.98</v>
+        <v>-39</v>
       </c>
       <c r="H17" s="25">
         <v>1.97</v>
       </c>
       <c r="I17" s="25">
-        <v>4</v>
-      </c>
-      <c r="J17" s="12">
-        <v>2.03</v>
+        <v>10.52</v>
+      </c>
+      <c r="J17" s="8">
+        <v>5.35</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="27" t="s">
+      <c r="F18" s="28">
+        <v>-39</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-44.3</v>
+      </c>
+      <c r="H18" s="28">
+        <v>3.17</v>
+      </c>
+      <c r="I18" s="28">
+        <v>5.3</v>
+      </c>
+      <c r="J18" s="15">
+        <v>1.67</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="25">
-        <v>-28.98</v>
-      </c>
-      <c r="G18" s="25">
-        <v>-37</v>
-      </c>
-      <c r="H18" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="I18" s="25">
-        <v>8.02</v>
-      </c>
-      <c r="J18" s="8">
-        <v>16.04</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="28">
-        <v>-37</v>
-      </c>
-      <c r="G19" s="28">
-        <v>-44.3</v>
-      </c>
-      <c r="H19" s="28">
-        <v>3.17</v>
-      </c>
-      <c r="I19" s="28">
-        <v>7.3</v>
-      </c>
-      <c r="J19" s="12">
-        <v>2.31</v>
-      </c>
-      <c r="K19" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-    </row>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1522,7 +1483,6 @@
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1533,7 +1493,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1556,31 +1516,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1600,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.18</v>
+        <v>-3.78</v>
       </c>
       <c r="G2" s="5">
         <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>3.18</v>
+        <v>3.78</v>
       </c>
       <c r="I2" s="8">
-        <v>9.54</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1626,48 +1586,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-3.18</v>
+        <v>-3.78</v>
       </c>
       <c r="F3" s="9">
-        <v>-3.78</v>
+        <v>-6.88</v>
       </c>
       <c r="G3" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="I3" s="12">
-        <v>1.5</v>
+        <v>3.1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-3.78</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
         <v>-6.88</v>
       </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-10.18</v>
+      </c>
+      <c r="G4" s="12">
         <v>1.17</v>
       </c>
-      <c r="H4" s="13">
-        <v>3.1</v>
-      </c>
-      <c r="I4" s="12">
-        <v>2.66</v>
+      <c r="H4" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="I4" s="15">
+        <v>2.83</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1678,25 +1638,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-6.88</v>
+        <v>-10.18</v>
       </c>
       <c r="F5" s="16">
-        <v>-10.18</v>
+        <v>-18.98</v>
       </c>
       <c r="G5" s="16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H5" s="16">
-        <v>3.3</v>
-      </c>
-      <c r="I5" s="12">
-        <v>1.74</v>
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="15">
+        <v>4.4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1707,25 +1667,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-10.18</v>
+        <v>-18.98</v>
       </c>
       <c r="F6" s="19">
-        <v>-18.98</v>
+        <v>-21.48</v>
       </c>
       <c r="G6" s="19">
         <v>2.17</v>
       </c>
       <c r="H6" s="19">
-        <v>8.8</v>
-      </c>
-      <c r="I6" s="12">
-        <v>4.06</v>
+        <v>2.5</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1.15</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1736,25 +1696,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-18.98</v>
+        <v>-21.48</v>
       </c>
       <c r="F7" s="22">
-        <v>-24.98</v>
+        <v>-28.48</v>
       </c>
       <c r="G7" s="22">
         <v>0.67</v>
       </c>
       <c r="H7" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="8">
-        <v>9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1765,25 +1725,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-24.98</v>
+        <v>-28.48</v>
       </c>
       <c r="F8" s="25">
-        <v>-37</v>
+        <v>-39</v>
       </c>
       <c r="G8" s="25">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="H8" s="25">
-        <v>12.02</v>
-      </c>
-      <c r="I8" s="12">
-        <v>4.87</v>
+        <v>10.52</v>
+      </c>
+      <c r="I8" s="8">
+        <v>5.35</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1794,13 +1754,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37</v>
+        <v>-39</v>
       </c>
       <c r="F9" s="28">
         <v>-44.3</v>
@@ -1809,15 +1769,15 @@
         <v>3.17</v>
       </c>
       <c r="H9" s="28">
-        <v>7.3</v>
-      </c>
-      <c r="I9" s="12">
-        <v>2.31</v>
+        <v>5.3</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1.67</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1826,7 +1786,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="33">
         <v>0</v>
@@ -1835,13 +1795,13 @@
         <v>-44.3</v>
       </c>
       <c r="G10" s="33">
-        <v>12.27</v>
+        <v>11.97</v>
       </c>
       <c r="H10" s="33">
         <v>44.3</v>
       </c>
       <c r="I10" s="33">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>
